--- a/01-Field-Discovery/06-noise/数据/课题06_十五组声学数据表与雷达图.xlsx
+++ b/01-Field-Discovery/06-noise/数据/课题06_十五组声学数据表与雷达图.xlsx
@@ -932,8 +932,8 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：Phyphox「声音振幅」原始包（20 Hz）　｜　判定依据：GB 3096-2008《声环境质量标准》　｜　昼间 6:00—22:00、夜间 22:00—6:00，本表早/中按昼间限值、晚按夜间限值评价　｜　实测 15 组，覆盖 5 点位 × 3 时段
-　｜　传感器：手机麦克风（OnePlus PLK110 / PKG110，Phyphox 1.2.1），未接标准声级计，绝对声级存在未量化偏差</t>
+          <t>数据来源：Phyphox「声音振幅」原始包（采样率约 9.2 Hz）　｜　判定依据：GB 3096-2008《声环境质量标准》　｜　昼间 6:00—22:00、夜间 22:00—6:00，本表早/中按昼间限值、晚按夜间限值评价　｜　15 组 · 5 点位 × 3 时段
+　｜　传感器：手机麦克风（OnePlus PLK110，Phyphox 1.2.1），未接标准声级计，绝对声级存在未量化偏差</t>
         </is>
       </c>
     </row>
@@ -1794,35 +1794,35 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>19:10:07</t>
+          <t>19:09:32</t>
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>55.5</v>
+        <v>115.3</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>464</v>
+        <v>1065</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>60.14</v>
+        <v>60.58</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>69.34999999999999</v>
+        <v>79.02</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>64.79000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="N15" s="8" t="n">
-        <v>58.45</v>
+        <v>58.67</v>
       </c>
       <c r="O15" s="8" t="n">
-        <v>59.67</v>
+        <v>59.74</v>
       </c>
       <c r="P15" s="8" t="n">
         <v>61.02</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>15.14</v>
+        <v>15.58</v>
       </c>
       <c r="R15" s="10" t="inlineStr">
         <is>
@@ -2269,10 +2269,10 @@
         <v>6.18</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>60.14</v>
+        <v>60.58</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>15.14</v>
+        <v>15.58</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -2536,7 +2536,7 @@
         <v>6.18</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>15.14</v>
+        <v>15.58</v>
       </c>
     </row>
     <row r="6">

--- a/01-Field-Discovery/06-noise/数据/课题06_十五组声学数据表与雷达图.xlsx
+++ b/01-Field-Discovery/06-noise/数据/课题06_十五组声学数据表与雷达图.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 光效参数" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01 十五组汇总'!$A$4:$R$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01 十五组汇总'!$A$4:$T$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -563,15 +563,15 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="16"/>
-          <min val="-15"/>
+          <max val="8"/>
+          <min val="-12"/>
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="5"/>
+        <majorUnit val="4"/>
       </valAx>
     </plotArea>
     <legend>
@@ -899,15 +899,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:T21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
@@ -920,6 +920,8 @@
     <col width="8" customWidth="1" min="16" max="16"/>
     <col width="9" customWidth="1" min="17" max="17"/>
     <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -932,7 +934,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：Phyphox「声音振幅」原始包（采样率约 9.2 Hz）　｜　判定依据：GB 3096-2008《声环境质量标准》　｜　昼间 6:00—22:00、夜间 22:00—6:00，本表早/中按昼间限值、晚按夜间限值评价　｜　15 组 · 5 点位 × 3 时段
+          <t>数据来源：Phyphox「声音振幅」原始包（采样率约 9.2 Hz）　｜　判定依据：GB 3096-2008《声环境质量标准》　｜　昼间 6:00—22:00、夜间 22:00—6:00；15 组实测时刻全部落在昼间区间，故判定一律用昼间限值，夜间限值仅作情景推演（最后两列）　｜　15 组 · 5 点位 × 3 时段
 　｜　传感器：手机麦克风（OnePlus PLK110，Phyphox 1.2.1），未接标准声级计，绝对声级存在未量化偏差</t>
         </is>
       </c>
@@ -950,8 +952,8 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>昼夜
-属性</t>
+          <t>标准
+归属</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -968,7 +970,7 @@
       <c r="F4" s="3" t="inlineStr">
         <is>
           <t>适用限值
-Leq dB(A)</t>
+(昼间) dB(A)</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1037,6 +1039,18 @@
           <t>判定</t>
         </is>
       </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>夜间限值
+(情景) dB(A)</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>情景 Δ
+(若按夜间)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="21" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -1109,6 +1123,12 @@
           <t>超标</t>
         </is>
       </c>
+      <c r="S5" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="T5" s="9" t="n">
+        <v>16.42</v>
+      </c>
     </row>
     <row r="6" ht="21" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -1181,6 +1201,12 @@
           <t>超标</t>
         </is>
       </c>
+      <c r="S6" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" s="9" t="n">
+        <v>12.49</v>
+      </c>
     </row>
     <row r="7" ht="21" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -1253,6 +1279,12 @@
           <t>达标</t>
         </is>
       </c>
+      <c r="S7" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="T7" s="9" t="n">
+        <v>8.460000000000001</v>
+      </c>
     </row>
     <row r="8" ht="21" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -1325,6 +1357,12 @@
           <t>超标</t>
         </is>
       </c>
+      <c r="S8" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" s="9" t="n">
+        <v>11.48</v>
+      </c>
     </row>
     <row r="9" ht="21" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -1397,6 +1435,12 @@
           <t>超标</t>
         </is>
       </c>
+      <c r="S9" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="T9" s="9" t="n">
+        <v>14.59</v>
+      </c>
     </row>
     <row r="10" ht="21" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -1469,6 +1513,12 @@
           <t>超标</t>
         </is>
       </c>
+      <c r="S10" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="T10" s="9" t="n">
+        <v>16.18</v>
+      </c>
     </row>
     <row r="11" ht="21" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -1541,6 +1591,12 @@
           <t>超标</t>
         </is>
       </c>
+      <c r="S11" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" s="9" t="n">
+        <v>13.98</v>
+      </c>
     </row>
     <row r="12" ht="21" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -1613,6 +1669,12 @@
           <t>达标</t>
         </is>
       </c>
+      <c r="S12" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="T12" s="9" t="n">
+        <v>2.34</v>
+      </c>
     </row>
     <row r="13" ht="21" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
@@ -1685,6 +1747,12 @@
           <t>超标</t>
         </is>
       </c>
+      <c r="S13" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" s="9" t="n">
+        <v>10.79</v>
+      </c>
     </row>
     <row r="14" ht="21" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -1757,6 +1825,12 @@
           <t>超标</t>
         </is>
       </c>
+      <c r="S14" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="T14" s="9" t="n">
+        <v>15.49</v>
+      </c>
     </row>
     <row r="15" ht="21" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -1771,7 +1845,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>夜间</t>
+          <t>昼间（19:00）</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -1785,7 +1859,7 @@
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
@@ -1822,12 +1896,18 @@
         <v>61.02</v>
       </c>
       <c r="Q15" s="9" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="R15" s="10" t="inlineStr">
+        <is>
+          <t>超标</t>
+        </is>
+      </c>
+      <c r="S15" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="T15" s="9" t="n">
         <v>15.58</v>
-      </c>
-      <c r="R15" s="10" t="inlineStr">
-        <is>
-          <t>超标</t>
-        </is>
       </c>
     </row>
     <row r="16" ht="21" customHeight="1">
@@ -1843,7 +1923,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>夜间</t>
+          <t>昼间（19:00）</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -1857,7 +1937,7 @@
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
@@ -1894,12 +1974,18 @@
         <v>65.03</v>
       </c>
       <c r="Q16" s="9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R16" s="10" t="inlineStr">
+        <is>
+          <t>超标</t>
+        </is>
+      </c>
+      <c r="S16" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" s="9" t="n">
         <v>12.75</v>
-      </c>
-      <c r="R16" s="10" t="inlineStr">
-        <is>
-          <t>超标</t>
-        </is>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
@@ -1915,7 +2001,7 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>夜间</t>
+          <t>昼间（19:00）</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -1929,7 +2015,7 @@
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
@@ -1966,12 +2052,18 @@
         <v>62.65</v>
       </c>
       <c r="Q17" s="9" t="n">
+        <v>-9.66</v>
+      </c>
+      <c r="R17" s="10" t="inlineStr">
+        <is>
+          <t>达标</t>
+        </is>
+      </c>
+      <c r="S17" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="T17" s="9" t="n">
         <v>5.34</v>
-      </c>
-      <c r="R17" s="10" t="inlineStr">
-        <is>
-          <t>超标</t>
-        </is>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
@@ -1987,7 +2079,7 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>夜间</t>
+          <t>昼间（19:00）</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -2001,7 +2093,7 @@
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
@@ -2038,12 +2130,18 @@
         <v>65.37</v>
       </c>
       <c r="Q18" s="9" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="R18" s="10" t="inlineStr">
+        <is>
+          <t>超标</t>
+        </is>
+      </c>
+      <c r="S18" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T18" s="9" t="n">
         <v>13.09</v>
-      </c>
-      <c r="R18" s="10" t="inlineStr">
-        <is>
-          <t>超标</t>
-        </is>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
@@ -2059,7 +2157,7 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>夜间</t>
+          <t>昼间（19:00）</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -2073,7 +2171,7 @@
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
@@ -2110,34 +2208,40 @@
         <v>61.18</v>
       </c>
       <c r="Q19" s="9" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="R19" s="10" t="inlineStr">
+        <is>
+          <t>超标</t>
+        </is>
+      </c>
+      <c r="S19" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="T19" s="9" t="n">
         <v>14.23</v>
-      </c>
-      <c r="R19" s="10" t="inlineStr">
-        <is>
-          <t>超标</t>
-        </is>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>统计：共 15 组　超标 13 组 / 达标 2 组　｜　昼间（早+中）10 组中超标 8 组；夜间 5 组全部超标</t>
+          <t>统计（昼间限值口径）：共 15 组　超标 12 组 / 达标 3 组（达标的 3 组都是主干道）；若改按夜间限值评价，则 15 组全部超标 —— 同一批声级，换把尺子结论就翻转</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R19"/>
+  <autoFilter ref="A4:T19"/>
   <mergeCells count="3">
-    <mergeCell ref="A2:R2"/>
-    <mergeCell ref="A21:R21"/>
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A21:T21"/>
+    <mergeCell ref="A2:T2"/>
   </mergeCells>
   <conditionalFormatting sqref="Q5:Q19">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-13"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="16"/>
+        <cfvo type="num" val="7"/>
         <color rgb="004A90D9"/>
         <color rgb="00FFFFFF"/>
         <color rgb="00E06666"/>
@@ -2272,7 +2376,7 @@
         <v>60.58</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>15.58</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -2308,7 +2412,7 @@
         <v>62.75</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>12.75</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -2344,7 +2448,7 @@
         <v>60.34</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>5.34</v>
+        <v>-9.66</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -2380,7 +2484,7 @@
         <v>63.09</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>13.09</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -2416,20 +2520,20 @@
         <v>59.23</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>14.23</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>读法：早 / 中 用昼间限值（55 / 60 / 70），晚用夜间限值（45 / 50 / 55）。Δ &gt; 0 即超标。主干道是 4a 类，限值最高，昼间两时段均达标；夜间限值降到 55，它的 Δ 由 −6.5 / −12.7 变成 +5.3。</t>
+          <t>读法：早 / 中 / 晚一律用昼间限值（55 / 60 / 70）。Δ &gt; 0 即超标。主干道是 4a 类，限值最高，三个时段全部达标（−6.5 / −12.7 / −9.7）；若改按夜间限值 55，它会由 −9.7 翻成 +5.3。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>关键现象：夜间 5 组全部超标，但夜间实测声级只比早间低 −3.1 ~ +1.6 dB。超标的主因是限值从昼间降到夜间整整 10 dB，而不是噪声变大了。</t>
+          <t>关键现象：三个时段的 Leq 只差 −3.1 ~ +1.6 dB，超标与否主要由「类别限值」决定；若改按夜间限值评价，15 组会全部超标 —— 差的那 10 dB 全部来自限值换挡。</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2640,7 @@
         <v>6.18</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>15.58</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="6">
@@ -2552,7 +2656,7 @@
         <v>3.98</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>12.75</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="7">
@@ -2568,7 +2672,7 @@
         <v>-12.66</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>5.34</v>
+        <v>-9.66</v>
       </c>
     </row>
     <row r="8">
@@ -2584,7 +2688,7 @@
         <v>0.79</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>13.09</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="9">
@@ -2600,7 +2704,7 @@
         <v>5.49</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>14.23</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -2648,21 +2752,21 @@
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>夜间三角形几乎整体包住昼间的两个——</t>
+          <t>三条曲线几乎贴在一起——同一批点位，早 / 中 / 晚的超出量</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>不是夜里变吵了，是夜间的尺子短了 10 dB。</t>
+          <t>相差不到 3 dB：傍晚并不比白天吵。若改按夜间限值重画一次，</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>（实测声级只差 −3.1 ~ +1.6 dB）</t>
+          <t>那圈会整体外扩 10 dB——外扩的是尺子，不是声音（见 01 页情景列）。</t>
         </is>
       </c>
     </row>
